--- a/bloomfield_truck_parking/Bloomfield_Truck_Parking_Model.xlsx
+++ b/bloomfield_truck_parking/Bloomfield_Truck_Parking_Model.xlsx
@@ -18,6 +18,7 @@
     <sheet name="Sensitivity" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Sources_Notes" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="Scale_Density" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Construction_Scale" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,7 +27,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="13">
     <numFmt numFmtId="164" formatCode="#,##0.00;(#,##0.00);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%;(0.0%);&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
@@ -35,6 +36,11 @@
     <numFmt numFmtId="169" formatCode="0.00&quot;x&quot;"/>
     <numFmt numFmtId="170" formatCode="$#,##0.00;($#,##0.00);&quot;-&quot;"/>
     <numFmt numFmtId="171" formatCode="0.00%;(0.00%);&quot;-&quot;"/>
+    <numFmt numFmtId="172" formatCode="0.000000"/>
+    <numFmt numFmtId="173" formatCode="0.000"/>
+    <numFmt numFmtId="174" formatCode="$#,##0.00;($#,##0.00)"/>
+    <numFmt numFmtId="175" formatCode="$#,##0;($#,##0)"/>
+    <numFmt numFmtId="176" formatCode="0.0%;(0.0%)"/>
   </numFmts>
   <fonts count="15">
     <font>
@@ -185,7 +191,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -297,6 +303,34 @@
     </xf>
     <xf numFmtId="166" fontId="8" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="8" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="174" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="175" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="174" fontId="8" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4080,6 +4114,2534 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J125"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="46" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Economies of Scale in Yard Construction  -  and the levers that beat them</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Splits the section into mobilisation / production / material, then prices design changes against the same basis. Calibrated so the base case reproduces the $9.45/SF used for S1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>A.  UNIT PRICES &amp; QUANTITIES</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Hot-mix asphalt, delivered</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>$ / ton</t>
+        </is>
+      </c>
+      <c r="C5" s="44" t="n">
+        <v>105</v>
+      </c>
+      <c r="J5" s="19" t="inlineStr">
+        <is>
+          <t>CT plant price for a binder/wearing mix. National HMA $80-160/t, average ~$110; CT construction runs ~1.32x national.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Processed aggregate base, delivered</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>$ / ton</t>
+        </is>
+      </c>
+      <c r="C6" s="44" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Recycled asphalt millings (RAP), delivered</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>$ / ton</t>
+        </is>
+      </c>
+      <c r="C7" s="44" t="n">
+        <v>16</v>
+      </c>
+      <c r="J7" s="19" t="inlineStr">
+        <is>
+          <t>Millings $7-25/ton in 2026; $15-35/ton delivered and placed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Triaxial geogrid, installed</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>$ / SY</t>
+        </is>
+      </c>
+      <c r="C8" s="44" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="J8" s="19" t="inlineStr">
+        <is>
+          <t>Biaxial $2-3/SY, triaxial $3-5/SY. Buys a 25-50% base-thickness reduction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>HMA thickness - base section</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>inches</t>
+        </is>
+      </c>
+      <c r="C9" s="83" t="n">
+        <v>5</v>
+      </c>
+      <c r="J9" s="19" t="inlineStr">
+        <is>
+          <t>3" binder + 2" wearing course.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Aggregate base thickness - base section</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>inches</t>
+        </is>
+      </c>
+      <c r="C10" s="83" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>HMA tonnage</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>tons / SF / inch</t>
+        </is>
+      </c>
+      <c r="C11" s="84" t="n">
+        <v>0.006222</v>
+      </c>
+      <c r="J11" s="19" t="inlineStr">
+        <is>
+          <t>~112 lb per SY per inch of compacted HMA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Aggregate tonnage</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>tons / SF / inch</t>
+        </is>
+      </c>
+      <c r="C12" s="84" t="n">
+        <v>0.005625</v>
+      </c>
+      <c r="J12" s="19" t="inlineStr">
+        <is>
+          <t>~135 lb per CF compacted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Paved area per stall</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="C13" s="42" t="n">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Share of yard that is stall, not aisle</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C14" s="39" t="n">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Base-case paved yard area</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="C15" s="10">
+        <f>Assumptions!$C$11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>B.  COST BEHAVIOUR OF THE BASE HEAVY-DUTY SECTION  ($ per SF of paved yard)</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="5" t="n"/>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Cost item</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr"/>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Mobilisation</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>Material %</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Clearing, grubbing, erosion control</t>
+        </is>
+      </c>
+      <c r="C19" s="44" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="D19" s="44" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="E19" s="44" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F19" s="79">
+        <f>SUM(C19:E19)</f>
+        <v/>
+      </c>
+      <c r="G19" s="50">
+        <f>IF(F19=0,0,E19/F19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Mass grading &amp; earthwork</t>
+        </is>
+      </c>
+      <c r="C20" s="44" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="D20" s="44" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="E20" s="44" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F20" s="79">
+        <f>SUM(C20:E20)</f>
+        <v/>
+      </c>
+      <c r="G20" s="50">
+        <f>IF(F20=0,0,E20/F20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Subgrade prep + aggregate base</t>
+        </is>
+      </c>
+      <c r="C21" s="44" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D21" s="44" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E21" s="44" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="F21" s="79">
+        <f>SUM(C21:E21)</f>
+        <v/>
+      </c>
+      <c r="G21" s="50">
+        <f>IF(F21=0,0,E21/F21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Bituminous surface course</t>
+        </is>
+      </c>
+      <c r="C22" s="44" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D22" s="44" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="E22" s="44" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="F22" s="79">
+        <f>SUM(C22:E22)</f>
+        <v/>
+      </c>
+      <c r="G22" s="50">
+        <f>IF(F22=0,0,E22/F22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Storm conveyance within yard</t>
+        </is>
+      </c>
+      <c r="C23" s="44" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D23" s="44" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E23" s="44" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F23" s="79">
+        <f>SUM(C23:E23)</f>
+        <v/>
+      </c>
+      <c r="G23" s="50">
+        <f>IF(F23=0,0,E23/F23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Striping, wheel stops, bollards</t>
+        </is>
+      </c>
+      <c r="C24" s="44" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D24" s="44" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E24" s="44" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F24" s="79">
+        <f>SUM(C24:E24)</f>
+        <v/>
+      </c>
+      <c r="G24" s="50">
+        <f>IF(F24=0,0,E24/F24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>$ per SF of paved yard</t>
+        </is>
+      </c>
+      <c r="C25" s="46">
+        <f>SUM(C19:C24)</f>
+        <v/>
+      </c>
+      <c r="D25" s="46">
+        <f>SUM(D19:D24)</f>
+        <v/>
+      </c>
+      <c r="E25" s="46">
+        <f>SUM(E19:E24)</f>
+        <v/>
+      </c>
+      <c r="F25" s="85">
+        <f>SUM(C25:E25)</f>
+        <v/>
+      </c>
+      <c r="G25" s="56">
+        <f>E25/F25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   share of yard construction</t>
+        </is>
+      </c>
+      <c r="C26" s="50">
+        <f>C25/$F$25</f>
+        <v/>
+      </c>
+      <c r="D26" s="50">
+        <f>D25/$F$25</f>
+        <v/>
+      </c>
+      <c r="E26" s="50">
+        <f>E25/$F$25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   $ per stall</t>
+        </is>
+      </c>
+      <c r="C27" s="49">
+        <f>C25*$C$13</f>
+        <v/>
+      </c>
+      <c r="D27" s="49">
+        <f>D25*$C$13</f>
+        <v/>
+      </c>
+      <c r="E27" s="49">
+        <f>E25*$C$13</f>
+        <v/>
+      </c>
+      <c r="F27" s="49">
+        <f>F25*$C$13</f>
+        <v/>
+      </c>
+      <c r="J27" s="48" t="inlineStr">
+        <is>
+          <t>Material is the majority of the section - and material is the part that barely responds to volume.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>Fixed mobilisation, all trades combined</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="C28" s="23">
+        <f>C25*$C$15</f>
+        <v/>
+      </c>
+      <c r="J28" s="19" t="inlineStr">
+        <is>
+          <t>Earthwork spread, paving train, milling machine, aggregate placement, striping crew, survey, testing. Incurred once per contract - this is the only genuinely fixed piece of the paving bill.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Base-case bulk tonnage (HMA + aggregate)</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>tons</t>
+        </is>
+      </c>
+      <c r="C29" s="36">
+        <f>$C$15*($C$11*$C$9+$C$12*$C$10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Bulk material content of the section</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>$ / SF</t>
+        </is>
+      </c>
+      <c r="C30" s="79">
+        <f>$C$11*$C$9*$C$5+$C$12*$C$10*$C$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Other material (does not tier)</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>$ / SF</t>
+        </is>
+      </c>
+      <c r="C31" s="79">
+        <f>E25-C30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>C.  SCALE PARAMETERS</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n"/>
+      <c r="C33" s="5" t="n"/>
+      <c r="D33" s="5" t="n"/>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="n"/>
+      <c r="G33" s="5" t="n"/>
+      <c r="H33" s="5" t="n"/>
+      <c r="I33" s="5" t="n"/>
+      <c r="J33" s="5" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Production learning exponent</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr"/>
+      <c r="C34" s="86" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="J34" s="19" t="inlineStr">
+        <is>
+          <t>Each doubling of paved area takes ~4.7% off the unit production rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Production rate floor</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>% of base</t>
+        </is>
+      </c>
+      <c r="C35" s="39" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="J35" s="19" t="inlineStr">
+        <is>
+          <t>Crews cannot beat their own maximum daily output, so the curve flattens.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Material volume tiers (tons / factor)</t>
+        </is>
+      </c>
+      <c r="C36" s="42" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D36" s="42" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E36" s="42" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F36" s="42" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>20,000+</t>
+        </is>
+      </c>
+      <c r="J36" s="19" t="inlineStr">
+        <is>
+          <t>Contractors ordering 500+ tons negotiate materially better pricing than 50-ton buyers; bulk orders above 20 tons typically see 5-15% off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" s="87" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" s="87" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="E37" s="87" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F37" s="87" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G37" s="87" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>Tier factor already captured at base scale</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr"/>
+      <c r="C38" s="88">
+        <f>IF($C$29&lt;=$C$36,$C$37,IF($C$29&lt;=$D$36,$D$37,IF($C$29&lt;=$E$36,$E$37,IF($C$29&lt;=$F$36,$F$37,$G$37))))</f>
+        <v/>
+      </c>
+      <c r="J38" s="19" t="inlineStr">
+        <is>
+          <t>The base case already sits in the best available tier, so tonnage pricing has nothing left to give as the site grows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>D.  THE SCALE CURVE  -  what volume alone can do</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n"/>
+      <c r="C40" s="5" t="n"/>
+      <c r="D40" s="5" t="n"/>
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="5" t="n"/>
+      <c r="G40" s="5" t="n"/>
+      <c r="H40" s="5" t="n"/>
+      <c r="I40" s="5" t="n"/>
+      <c r="J40" s="5" t="n"/>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="4" t="inlineStr"/>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Paved acres</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Stalls</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>Bulk tons</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>Mobilise $/SF</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>Production $/SF</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>Material $/SF</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>Total $/SF</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>$ / stall</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>vs base</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="89" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" s="82">
+        <f>($B42*43560)/$C$13</f>
+        <v/>
+      </c>
+      <c r="D42" s="82">
+        <f>($B42*43560)*($C$11*$C$9+$C$12*$C$10)</f>
+        <v/>
+      </c>
+      <c r="E42" s="90">
+        <f>$C$28/($B42*43560)</f>
+        <v/>
+      </c>
+      <c r="F42" s="90">
+        <f>$D$25*MAX($C$35,(($B42*43560)/$C$15)^-$C$34)</f>
+        <v/>
+      </c>
+      <c r="G42" s="90">
+        <f>(IF($D42&lt;=$C$36,$C$37,IF($D42&lt;=$D$36,$D$37,IF($D42&lt;=$E$36,$E$37,IF($D42&lt;=$F$36,$F$37,$G$37)))))/$C$38*$C$30+$C$31</f>
+        <v/>
+      </c>
+      <c r="H42" s="90">
+        <f>SUM(E42:G42)</f>
+        <v/>
+      </c>
+      <c r="I42" s="73">
+        <f>H42*$C$13</f>
+        <v/>
+      </c>
+      <c r="J42" s="91">
+        <f>H42/$H$46-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="89" t="n">
+        <v>2</v>
+      </c>
+      <c r="C43" s="82">
+        <f>($B43*43560)/$C$13</f>
+        <v/>
+      </c>
+      <c r="D43" s="82">
+        <f>($B43*43560)*($C$11*$C$9+$C$12*$C$10)</f>
+        <v/>
+      </c>
+      <c r="E43" s="90">
+        <f>$C$28/($B43*43560)</f>
+        <v/>
+      </c>
+      <c r="F43" s="90">
+        <f>$D$25*MAX($C$35,(($B43*43560)/$C$15)^-$C$34)</f>
+        <v/>
+      </c>
+      <c r="G43" s="90">
+        <f>(IF($D43&lt;=$C$36,$C$37,IF($D43&lt;=$D$36,$D$37,IF($D43&lt;=$E$36,$E$37,IF($D43&lt;=$F$36,$F$37,$G$37)))))/$C$38*$C$30+$C$31</f>
+        <v/>
+      </c>
+      <c r="H43" s="90">
+        <f>SUM(E43:G43)</f>
+        <v/>
+      </c>
+      <c r="I43" s="73">
+        <f>H43*$C$13</f>
+        <v/>
+      </c>
+      <c r="J43" s="91">
+        <f>H43/$H$46-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="89" t="n">
+        <v>3</v>
+      </c>
+      <c r="C44" s="82">
+        <f>($B44*43560)/$C$13</f>
+        <v/>
+      </c>
+      <c r="D44" s="82">
+        <f>($B44*43560)*($C$11*$C$9+$C$12*$C$10)</f>
+        <v/>
+      </c>
+      <c r="E44" s="90">
+        <f>$C$28/($B44*43560)</f>
+        <v/>
+      </c>
+      <c r="F44" s="90">
+        <f>$D$25*MAX($C$35,(($B44*43560)/$C$15)^-$C$34)</f>
+        <v/>
+      </c>
+      <c r="G44" s="90">
+        <f>(IF($D44&lt;=$C$36,$C$37,IF($D44&lt;=$D$36,$D$37,IF($D44&lt;=$E$36,$E$37,IF($D44&lt;=$F$36,$F$37,$G$37)))))/$C$38*$C$30+$C$31</f>
+        <v/>
+      </c>
+      <c r="H44" s="90">
+        <f>SUM(E44:G44)</f>
+        <v/>
+      </c>
+      <c r="I44" s="73">
+        <f>H44*$C$13</f>
+        <v/>
+      </c>
+      <c r="J44" s="91">
+        <f>H44/$H$46-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="89" t="n">
+        <v>5</v>
+      </c>
+      <c r="C45" s="82">
+        <f>($B45*43560)/$C$13</f>
+        <v/>
+      </c>
+      <c r="D45" s="82">
+        <f>($B45*43560)*($C$11*$C$9+$C$12*$C$10)</f>
+        <v/>
+      </c>
+      <c r="E45" s="90">
+        <f>$C$28/($B45*43560)</f>
+        <v/>
+      </c>
+      <c r="F45" s="90">
+        <f>$D$25*MAX($C$35,(($B45*43560)/$C$15)^-$C$34)</f>
+        <v/>
+      </c>
+      <c r="G45" s="90">
+        <f>(IF($D45&lt;=$C$36,$C$37,IF($D45&lt;=$D$36,$D$37,IF($D45&lt;=$E$36,$E$37,IF($D45&lt;=$F$36,$F$37,$G$37)))))/$C$38*$C$30+$C$31</f>
+        <v/>
+      </c>
+      <c r="H45" s="90">
+        <f>SUM(E45:G45)</f>
+        <v/>
+      </c>
+      <c r="I45" s="73">
+        <f>H45*$C$13</f>
+        <v/>
+      </c>
+      <c r="J45" s="91">
+        <f>H45/$H$46-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="68" t="inlineStr">
+        <is>
+          <t>base case  -&gt;</t>
+        </is>
+      </c>
+      <c r="B46" s="89" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="C46" s="82">
+        <f>($B46*43560)/$C$13</f>
+        <v/>
+      </c>
+      <c r="D46" s="82">
+        <f>($B46*43560)*($C$11*$C$9+$C$12*$C$10)</f>
+        <v/>
+      </c>
+      <c r="E46" s="90">
+        <f>$C$28/($B46*43560)</f>
+        <v/>
+      </c>
+      <c r="F46" s="90">
+        <f>$D$25*MAX($C$35,(($B46*43560)/$C$15)^-$C$34)</f>
+        <v/>
+      </c>
+      <c r="G46" s="90">
+        <f>(IF($D46&lt;=$C$36,$C$37,IF($D46&lt;=$D$36,$D$37,IF($D46&lt;=$E$36,$E$37,IF($D46&lt;=$F$36,$F$37,$G$37)))))/$C$38*$C$30+$C$31</f>
+        <v/>
+      </c>
+      <c r="H46" s="90">
+        <f>SUM(E46:G46)</f>
+        <v/>
+      </c>
+      <c r="I46" s="73">
+        <f>H46*$C$13</f>
+        <v/>
+      </c>
+      <c r="J46" s="91">
+        <f>H46/$H$46-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="89" t="n">
+        <v>10</v>
+      </c>
+      <c r="C47" s="82">
+        <f>($B47*43560)/$C$13</f>
+        <v/>
+      </c>
+      <c r="D47" s="82">
+        <f>($B47*43560)*($C$11*$C$9+$C$12*$C$10)</f>
+        <v/>
+      </c>
+      <c r="E47" s="90">
+        <f>$C$28/($B47*43560)</f>
+        <v/>
+      </c>
+      <c r="F47" s="90">
+        <f>$D$25*MAX($C$35,(($B47*43560)/$C$15)^-$C$34)</f>
+        <v/>
+      </c>
+      <c r="G47" s="90">
+        <f>(IF($D47&lt;=$C$36,$C$37,IF($D47&lt;=$D$36,$D$37,IF($D47&lt;=$E$36,$E$37,IF($D47&lt;=$F$36,$F$37,$G$37)))))/$C$38*$C$30+$C$31</f>
+        <v/>
+      </c>
+      <c r="H47" s="90">
+        <f>SUM(E47:G47)</f>
+        <v/>
+      </c>
+      <c r="I47" s="73">
+        <f>H47*$C$13</f>
+        <v/>
+      </c>
+      <c r="J47" s="91">
+        <f>H47/$H$46-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="89" t="n">
+        <v>15</v>
+      </c>
+      <c r="C48" s="82">
+        <f>($B48*43560)/$C$13</f>
+        <v/>
+      </c>
+      <c r="D48" s="82">
+        <f>($B48*43560)*($C$11*$C$9+$C$12*$C$10)</f>
+        <v/>
+      </c>
+      <c r="E48" s="90">
+        <f>$C$28/($B48*43560)</f>
+        <v/>
+      </c>
+      <c r="F48" s="90">
+        <f>$D$25*MAX($C$35,(($B48*43560)/$C$15)^-$C$34)</f>
+        <v/>
+      </c>
+      <c r="G48" s="90">
+        <f>(IF($D48&lt;=$C$36,$C$37,IF($D48&lt;=$D$36,$D$37,IF($D48&lt;=$E$36,$E$37,IF($D48&lt;=$F$36,$F$37,$G$37)))))/$C$38*$C$30+$C$31</f>
+        <v/>
+      </c>
+      <c r="H48" s="90">
+        <f>SUM(E48:G48)</f>
+        <v/>
+      </c>
+      <c r="I48" s="73">
+        <f>H48*$C$13</f>
+        <v/>
+      </c>
+      <c r="J48" s="91">
+        <f>H48/$H$46-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="89" t="n">
+        <v>20</v>
+      </c>
+      <c r="C49" s="82">
+        <f>($B49*43560)/$C$13</f>
+        <v/>
+      </c>
+      <c r="D49" s="82">
+        <f>($B49*43560)*($C$11*$C$9+$C$12*$C$10)</f>
+        <v/>
+      </c>
+      <c r="E49" s="90">
+        <f>$C$28/($B49*43560)</f>
+        <v/>
+      </c>
+      <c r="F49" s="90">
+        <f>$D$25*MAX($C$35,(($B49*43560)/$C$15)^-$C$34)</f>
+        <v/>
+      </c>
+      <c r="G49" s="90">
+        <f>(IF($D49&lt;=$C$36,$C$37,IF($D49&lt;=$D$36,$D$37,IF($D49&lt;=$E$36,$E$37,IF($D49&lt;=$F$36,$F$37,$G$37)))))/$C$38*$C$30+$C$31</f>
+        <v/>
+      </c>
+      <c r="H49" s="90">
+        <f>SUM(E49:G49)</f>
+        <v/>
+      </c>
+      <c r="I49" s="73">
+        <f>H49*$C$13</f>
+        <v/>
+      </c>
+      <c r="J49" s="91">
+        <f>H49/$H$46-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="89" t="n">
+        <v>30</v>
+      </c>
+      <c r="C50" s="82">
+        <f>($B50*43560)/$C$13</f>
+        <v/>
+      </c>
+      <c r="D50" s="82">
+        <f>($B50*43560)*($C$11*$C$9+$C$12*$C$10)</f>
+        <v/>
+      </c>
+      <c r="E50" s="90">
+        <f>$C$28/($B50*43560)</f>
+        <v/>
+      </c>
+      <c r="F50" s="90">
+        <f>$D$25*MAX($C$35,(($B50*43560)/$C$15)^-$C$34)</f>
+        <v/>
+      </c>
+      <c r="G50" s="90">
+        <f>(IF($D50&lt;=$C$36,$C$37,IF($D50&lt;=$D$36,$D$37,IF($D50&lt;=$E$36,$E$37,IF($D50&lt;=$F$36,$F$37,$G$37)))))/$C$38*$C$30+$C$31</f>
+        <v/>
+      </c>
+      <c r="H50" s="90">
+        <f>SUM(E50:G50)</f>
+        <v/>
+      </c>
+      <c r="I50" s="73">
+        <f>H50*$C$13</f>
+        <v/>
+      </c>
+      <c r="J50" s="91">
+        <f>H50/$H$46-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="89" t="n">
+        <v>50</v>
+      </c>
+      <c r="C51" s="82">
+        <f>($B51*43560)/$C$13</f>
+        <v/>
+      </c>
+      <c r="D51" s="82">
+        <f>($B51*43560)*($C$11*$C$9+$C$12*$C$10)</f>
+        <v/>
+      </c>
+      <c r="E51" s="90">
+        <f>$C$28/($B51*43560)</f>
+        <v/>
+      </c>
+      <c r="F51" s="90">
+        <f>$D$25*MAX($C$35,(($B51*43560)/$C$15)^-$C$34)</f>
+        <v/>
+      </c>
+      <c r="G51" s="90">
+        <f>(IF($D51&lt;=$C$36,$C$37,IF($D51&lt;=$D$36,$D$37,IF($D51&lt;=$E$36,$E$37,IF($D51&lt;=$F$36,$F$37,$G$37)))))/$C$38*$C$30+$C$31</f>
+        <v/>
+      </c>
+      <c r="H51" s="90">
+        <f>SUM(E51:G51)</f>
+        <v/>
+      </c>
+      <c r="I51" s="73">
+        <f>H51*$C$13</f>
+        <v/>
+      </c>
+      <c r="J51" s="91">
+        <f>H51/$H$46-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="48" t="inlineStr">
+        <is>
+          <t>Scale in construction is bounded: material is the majority of the section and the base case already sits in the top volume tier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>E.  SPECIFICATION LEVERS  -  changing what gets built, not how much</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n"/>
+      <c r="C54" s="5" t="n"/>
+      <c r="D54" s="5" t="n"/>
+      <c r="E54" s="5" t="n"/>
+      <c r="F54" s="5" t="n"/>
+      <c r="G54" s="5" t="n"/>
+      <c r="H54" s="5" t="n"/>
+      <c r="I54" s="5" t="n"/>
+      <c r="J54" s="5" t="n"/>
+    </row>
+    <row r="55" ht="26" customHeight="1">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Lever</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr"/>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>$ / SF</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>$ / stall</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>% of yard</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr"/>
+      <c r="G55" s="3" t="inlineStr"/>
+      <c r="H55" s="3" t="inlineStr"/>
+      <c r="I55" s="3" t="inlineStr"/>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="30" customHeight="1">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>Geogrid - aggregate base 12" to 8"</t>
+        </is>
+      </c>
+      <c r="C56" s="92">
+        <f>-(4*$C$12*$C$6)-4*($D$25*0+0.86/$C$10)+$C$8/9</f>
+        <v/>
+      </c>
+      <c r="D56" s="93">
+        <f>C56*$C$13</f>
+        <v/>
+      </c>
+      <c r="E56" s="94">
+        <f>C56/$F$25</f>
+        <v/>
+      </c>
+      <c r="J56" s="19" t="inlineStr">
+        <is>
+          <t>Triaxial geogrid at ~$4.25/SY installed buys a 25-50% base reduction, and de-risks soft subgrade. Modest here because CT aggregate is cheap relative to the grid; the payoff is much larger where undercut would otherwise be needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="30" customHeight="1">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>25% RAP content in the HMA mix</t>
+        </is>
+      </c>
+      <c r="C57" s="92">
+        <f>-0.10*($C$11*$C$9*$C$5)</f>
+        <v/>
+      </c>
+      <c r="D57" s="93">
+        <f>C57*$C$13</f>
+        <v/>
+      </c>
+      <c r="E57" s="94">
+        <f>C57/$F$25</f>
+        <v/>
+      </c>
+      <c r="J57" s="19" t="inlineStr">
+        <is>
+          <t>Recycled asphalt pavement in the mix takes 8-15% off mix price. Confirm the nearest plant's RAP capability before assuming it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="30" customHeight="1">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>Millings for the lower 6" of base</t>
+        </is>
+      </c>
+      <c r="C58" s="92">
+        <f>-6*$C$12*($C$6-$C$7)</f>
+        <v/>
+      </c>
+      <c r="D58" s="93">
+        <f>C58*$C$13</f>
+        <v/>
+      </c>
+      <c r="E58" s="94">
+        <f>C58/$F$25</f>
+        <v/>
+      </c>
+      <c r="J58" s="19" t="inlineStr">
+        <is>
+          <t>Crushed RAP against processed aggregate. Supply is opportunistic - it depends on what milling jobs are running nearby.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="30" customHeight="1">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>Balanced cut/fill - no import, no export</t>
+        </is>
+      </c>
+      <c r="C59" s="92">
+        <f>-0.45</f>
+        <v/>
+      </c>
+      <c r="D59" s="93">
+        <f>C59*$C$13</f>
+        <v/>
+      </c>
+      <c r="E59" s="94">
+        <f>C59/$F$25</f>
+        <v/>
+      </c>
+      <c r="J59" s="19" t="inlineStr">
+        <is>
+          <t>Removes both the import-fill material and the export haul. Has to be designed in from the first grading plan; it is not a change order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="30" customHeight="1">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>Thinner HMA in stall areas only (5" to 4")</t>
+        </is>
+      </c>
+      <c r="C60" s="92">
+        <f>-$C$14*($C$11*$C$5+(1.11/$C$9))</f>
+        <v/>
+      </c>
+      <c r="D60" s="93">
+        <f>C60*$C$13</f>
+        <v/>
+      </c>
+      <c r="E60" s="94">
+        <f>C60/$F$25</f>
+        <v/>
+      </c>
+      <c r="J60" s="19" t="inlineStr">
+        <is>
+          <t>Drive aisles keep the full section. Real rutting risk under static trailer loads - pair it with landing-gear pads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="30" customHeight="1">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>Hybrid surface: paved aisles, millings stalls</t>
+        </is>
+      </c>
+      <c r="C61" s="92">
+        <f>-2.75</f>
+        <v/>
+      </c>
+      <c r="D61" s="93">
+        <f>C61*$C$13</f>
+        <v/>
+      </c>
+      <c r="E61" s="94">
+        <f>C61/$F$25</f>
+        <v/>
+      </c>
+      <c r="J61" s="19" t="inlineStr">
+        <is>
+          <t>The S2 specification. Largest single lever by a wide margin, and it also shrinks the stormwater basin because the stall area is far less impervious.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="30" customHeight="1">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>On-site crush &amp; reuse of demo concrete/pavement</t>
+        </is>
+      </c>
+      <c r="C62" s="92">
+        <f>-0.35</f>
+        <v/>
+      </c>
+      <c r="D62" s="93">
+        <f>C62*$C$13</f>
+        <v/>
+      </c>
+      <c r="E62" s="94">
+        <f>C62/$F$25</f>
+        <v/>
+      </c>
+      <c r="J62" s="19" t="inlineStr">
+        <is>
+          <t>Only where a structure or existing pavement is coming out. Avoids the export haul AND the import purchase - it counts twice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="30" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>ADD: concrete landing-gear pads, 48 SF/stall</t>
+        </is>
+      </c>
+      <c r="C63" s="92">
+        <f>48*14/$C$13</f>
+        <v/>
+      </c>
+      <c r="D63" s="93">
+        <f>C63*$C$13</f>
+        <v/>
+      </c>
+      <c r="E63" s="94">
+        <f>C63/$F$25</f>
+        <v/>
+      </c>
+      <c r="J63" s="19" t="inlineStr">
+        <is>
+          <t>A deliberate cost ADD. Stops the punch-through failure at the trailer landing gear that otherwise drives premature reconstruction of the stall.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>F.  PACKAGES  -  1 includes the lever, 0 excludes it</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="n"/>
+      <c r="C65" s="5" t="n"/>
+      <c r="D65" s="5" t="n"/>
+      <c r="E65" s="5" t="n"/>
+      <c r="F65" s="5" t="n"/>
+      <c r="G65" s="5" t="n"/>
+      <c r="H65" s="5" t="n"/>
+      <c r="I65" s="5" t="n"/>
+      <c r="J65" s="5" t="n"/>
+    </row>
+    <row r="66" ht="32" customHeight="1">
+      <c r="A66" s="59" t="inlineStr">
+        <is>
+          <t>Lever</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>Base section</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>A  Value-engineer</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>B  A + thin stalls</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>C  Hybrid (S2)</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>D  Hybrid + all</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="95" t="inlineStr">
+        <is>
+          <t>Geogrid - aggregate base 12" to 8"</t>
+        </is>
+      </c>
+      <c r="C67" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" s="96" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" s="96" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="96" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="95" t="inlineStr">
+        <is>
+          <t>25% RAP content in the HMA mix</t>
+        </is>
+      </c>
+      <c r="C68" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D68" s="96" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" s="96" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" s="96" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="95" t="inlineStr">
+        <is>
+          <t>Millings for the lower 6" of base</t>
+        </is>
+      </c>
+      <c r="C69" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="96" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" s="96" t="n">
+        <v>1</v>
+      </c>
+      <c r="F69" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" s="96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="95" t="inlineStr">
+        <is>
+          <t>Balanced cut/fill - no import, no export</t>
+        </is>
+      </c>
+      <c r="C70" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="96" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" s="96" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" s="96" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="95" t="inlineStr">
+        <is>
+          <t>Thinner HMA in stall areas only (5" to 4")</t>
+        </is>
+      </c>
+      <c r="C71" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="96" t="n">
+        <v>1</v>
+      </c>
+      <c r="F71" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="95" t="inlineStr">
+        <is>
+          <t>Hybrid surface: paved aisles, millings stalls</t>
+        </is>
+      </c>
+      <c r="C72" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="96" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" s="96" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="95" t="inlineStr">
+        <is>
+          <t>On-site crush &amp; reuse of demo concrete/pavement</t>
+        </is>
+      </c>
+      <c r="C73" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="95" t="inlineStr">
+        <is>
+          <t>ADD: concrete landing-gear pads, 48 SF/stall</t>
+        </is>
+      </c>
+      <c r="C74" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="96" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" s="96" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="9" t="inlineStr">
+        <is>
+          <t>Package delta</t>
+        </is>
+      </c>
+      <c r="C75" s="97">
+        <f>SUMPRODUCT(C67:C74,$C$56:$C$63)</f>
+        <v/>
+      </c>
+      <c r="D75" s="97">
+        <f>SUMPRODUCT(D67:D74,$C$56:$C$63)</f>
+        <v/>
+      </c>
+      <c r="E75" s="97">
+        <f>SUMPRODUCT(E67:E74,$C$56:$C$63)</f>
+        <v/>
+      </c>
+      <c r="F75" s="97">
+        <f>SUMPRODUCT(F67:F74,$C$56:$C$63)</f>
+        <v/>
+      </c>
+      <c r="G75" s="97">
+        <f>SUMPRODUCT(G67:G74,$C$56:$C$63)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="9" t="inlineStr">
+        <is>
+          <t>Yard construction $/SF</t>
+        </is>
+      </c>
+      <c r="C76" s="98">
+        <f>$F$25+C75</f>
+        <v/>
+      </c>
+      <c r="D76" s="98">
+        <f>$F$25+D75</f>
+        <v/>
+      </c>
+      <c r="E76" s="98">
+        <f>$F$25+E75</f>
+        <v/>
+      </c>
+      <c r="F76" s="98">
+        <f>$F$25+F75</f>
+        <v/>
+      </c>
+      <c r="G76" s="98">
+        <f>$F$25+G75</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="9" t="inlineStr">
+        <is>
+          <t>Yard construction $/stall</t>
+        </is>
+      </c>
+      <c r="C77" s="18">
+        <f>C76*$C$13</f>
+        <v/>
+      </c>
+      <c r="D77" s="18">
+        <f>D76*$C$13</f>
+        <v/>
+      </c>
+      <c r="E77" s="18">
+        <f>E76*$C$13</f>
+        <v/>
+      </c>
+      <c r="F77" s="18">
+        <f>F76*$C$13</f>
+        <v/>
+      </c>
+      <c r="G77" s="18">
+        <f>G76*$C$13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   cut vs. base section</t>
+        </is>
+      </c>
+      <c r="C78" s="94">
+        <f>C76/$C$76-1</f>
+        <v/>
+      </c>
+      <c r="D78" s="94">
+        <f>D76/$C$76-1</f>
+        <v/>
+      </c>
+      <c r="E78" s="94">
+        <f>E76/$C$76-1</f>
+        <v/>
+      </c>
+      <c r="F78" s="94">
+        <f>F76/$C$76-1</f>
+        <v/>
+      </c>
+      <c r="G78" s="94">
+        <f>G76/$C$76-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>G.  NON-LAND FIXED COST  -  the larger prize, and it scales harder</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="n"/>
+      <c r="C80" s="5" t="n"/>
+      <c r="D80" s="5" t="n"/>
+      <c r="E80" s="5" t="n"/>
+      <c r="F80" s="5" t="n"/>
+      <c r="G80" s="5" t="n"/>
+      <c r="H80" s="5" t="n"/>
+      <c r="I80" s="5" t="n"/>
+      <c r="J80" s="5" t="n"/>
+    </row>
+    <row r="81" ht="26" customHeight="1">
+      <c r="A81" s="19" t="inlineStr">
+        <is>
+          <t>At 216 stalls, S2 carries $21,813/stall of fixed cost, of which only $8,280 is land. The remaining non-land fixed cost exceeds the entire yard construction bill per stall - and most of it does not grow with the site at all.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr"/>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>$ at base scale</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>Behaviour</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr"/>
+      <c r="F82" s="3" t="inlineStr"/>
+      <c r="G82" s="3" t="inlineStr"/>
+      <c r="H82" s="3" t="inlineStr"/>
+      <c r="I82" s="3" t="inlineStr"/>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>Pre-development, design, entitlement</t>
+        </is>
+      </c>
+      <c r="C83" s="40" t="n">
+        <v>445000</v>
+      </c>
+      <c r="D83" s="99" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>Utility service &amp; transformer</t>
+        </is>
+      </c>
+      <c r="C84" s="40" t="n">
+        <v>185000</v>
+      </c>
+      <c r="D84" s="99" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>Security head-end (NVR, analytics)</t>
+        </is>
+      </c>
+      <c r="C85" s="40" t="n">
+        <v>175000</v>
+      </c>
+      <c r="D85" s="99" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>Site entry, apron, turn lane</t>
+        </is>
+      </c>
+      <c r="C86" s="40" t="n">
+        <v>175000</v>
+      </c>
+      <c r="D86" s="99" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>Gatehouse / driver services</t>
+        </is>
+      </c>
+      <c r="C87" s="40" t="n">
+        <v>145000</v>
+      </c>
+      <c r="D87" s="99" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>Automated gates &amp; access control</t>
+        </is>
+      </c>
+      <c r="C88" s="40" t="n">
+        <v>145000</v>
+      </c>
+      <c r="D88" s="99" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>Demolition &amp; clearing outside yard</t>
+        </is>
+      </c>
+      <c r="C89" s="40" t="n">
+        <v>95000</v>
+      </c>
+      <c r="D89" s="99" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>Perimeter fence</t>
+        </is>
+      </c>
+      <c r="C90" s="40" t="n">
+        <v>137280</v>
+      </c>
+      <c r="D90" s="99" t="inlineStr">
+        <is>
+          <t>perimeter</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>Landscaping &amp; buffer plantings</t>
+        </is>
+      </c>
+      <c r="C91" s="40" t="n">
+        <v>105000</v>
+      </c>
+      <c r="D91" s="99" t="inlineStr">
+        <is>
+          <t>perimeter</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>Stormwater basin &amp; treatment</t>
+        </is>
+      </c>
+      <c r="C92" s="40" t="n">
+        <v>355000</v>
+      </c>
+      <c r="D92" s="99" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="9" t="inlineStr">
+        <is>
+          <t>Flat per site - does not grow at all</t>
+        </is>
+      </c>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="C93" s="23">
+        <f>SUMIF($D$83:$D$92,"flat",$C$83:$C$92)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="9" t="inlineStr">
+        <is>
+          <t>Grows with perimeter (square root of area)</t>
+        </is>
+      </c>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="C94" s="23">
+        <f>SUMIF($D$83:$D$92,"perimeter",$C$83:$C$92)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="9" t="inlineStr">
+        <is>
+          <t>Grows with impervious area - no economy of scale</t>
+        </is>
+      </c>
+      <c r="B95" s="7" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="C95" s="23">
+        <f>SUMIF($D$83:$D$92,"area",$C$83:$C$92)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>Soft-cost loadings + contingency</t>
+        </is>
+      </c>
+      <c r="B96" s="7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C96" s="100" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="J96" s="19" t="inlineStr">
+        <is>
+          <t>5% soft loadings plus 12% contingency, applied to the direct items above.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>Stalls at base scale</t>
+        </is>
+      </c>
+      <c r="B97" s="7" t="inlineStr">
+        <is>
+          <t>stalls</t>
+        </is>
+      </c>
+      <c r="C97" s="42" t="n">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="99" ht="30" customHeight="1">
+      <c r="A99" s="4" t="inlineStr"/>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>Stalls</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>Gross acres</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>Flat $/stall</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>Perimeter $/stall</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>Stormwater $/stall</t>
+        </is>
+      </c>
+      <c r="G99" s="4" t="inlineStr">
+        <is>
+          <t>Total $/stall</t>
+        </is>
+      </c>
+      <c r="H99" s="4" t="inlineStr">
+        <is>
+          <t>vs base</t>
+        </is>
+      </c>
+      <c r="I99" s="4" t="inlineStr"/>
+      <c r="J99" s="4" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="B100" s="101" t="n">
+        <v>86</v>
+      </c>
+      <c r="C100" s="102">
+        <f>$B100*$C$13/Assumptions!$D$7/43560</f>
+        <v/>
+      </c>
+      <c r="D100" s="73">
+        <f>$C$93*$C$96/$B100</f>
+        <v/>
+      </c>
+      <c r="E100" s="73">
+        <f>$C$94*($B100/$C$97)^0.5*$C$96/$B100</f>
+        <v/>
+      </c>
+      <c r="F100" s="73">
+        <f>$C$95*($B100/$C$97)*$C$96/$B100</f>
+        <v/>
+      </c>
+      <c r="G100" s="103">
+        <f>SUM(D100:F100)</f>
+        <v/>
+      </c>
+      <c r="H100" s="104">
+        <f>G100/$G$102-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" s="101" t="n">
+        <v>150</v>
+      </c>
+      <c r="C101" s="102">
+        <f>$B101*$C$13/Assumptions!$D$7/43560</f>
+        <v/>
+      </c>
+      <c r="D101" s="73">
+        <f>$C$93*$C$96/$B101</f>
+        <v/>
+      </c>
+      <c r="E101" s="73">
+        <f>$C$94*($B101/$C$97)^0.5*$C$96/$B101</f>
+        <v/>
+      </c>
+      <c r="F101" s="73">
+        <f>$C$95*($B101/$C$97)*$C$96/$B101</f>
+        <v/>
+      </c>
+      <c r="G101" s="103">
+        <f>SUM(D101:F101)</f>
+        <v/>
+      </c>
+      <c r="H101" s="104">
+        <f>G101/$G$102-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="68" t="inlineStr">
+        <is>
+          <t>base case  -&gt;</t>
+        </is>
+      </c>
+      <c r="B102" s="101" t="n">
+        <v>216</v>
+      </c>
+      <c r="C102" s="102">
+        <f>$B102*$C$13/Assumptions!$D$7/43560</f>
+        <v/>
+      </c>
+      <c r="D102" s="73">
+        <f>$C$93*$C$96/$B102</f>
+        <v/>
+      </c>
+      <c r="E102" s="73">
+        <f>$C$94*($B102/$C$97)^0.5*$C$96/$B102</f>
+        <v/>
+      </c>
+      <c r="F102" s="73">
+        <f>$C$95*($B102/$C$97)*$C$96/$B102</f>
+        <v/>
+      </c>
+      <c r="G102" s="103">
+        <f>SUM(D102:F102)</f>
+        <v/>
+      </c>
+      <c r="H102" s="104">
+        <f>G102/$G$102-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" s="101" t="n">
+        <v>300</v>
+      </c>
+      <c r="C103" s="102">
+        <f>$B103*$C$13/Assumptions!$D$7/43560</f>
+        <v/>
+      </c>
+      <c r="D103" s="73">
+        <f>$C$93*$C$96/$B103</f>
+        <v/>
+      </c>
+      <c r="E103" s="73">
+        <f>$C$94*($B103/$C$97)^0.5*$C$96/$B103</f>
+        <v/>
+      </c>
+      <c r="F103" s="73">
+        <f>$C$95*($B103/$C$97)*$C$96/$B103</f>
+        <v/>
+      </c>
+      <c r="G103" s="103">
+        <f>SUM(D103:F103)</f>
+        <v/>
+      </c>
+      <c r="H103" s="104">
+        <f>G103/$G$102-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" s="101" t="n">
+        <v>450</v>
+      </c>
+      <c r="C104" s="102">
+        <f>$B104*$C$13/Assumptions!$D$7/43560</f>
+        <v/>
+      </c>
+      <c r="D104" s="73">
+        <f>$C$93*$C$96/$B104</f>
+        <v/>
+      </c>
+      <c r="E104" s="73">
+        <f>$C$94*($B104/$C$97)^0.5*$C$96/$B104</f>
+        <v/>
+      </c>
+      <c r="F104" s="73">
+        <f>$C$95*($B104/$C$97)*$C$96/$B104</f>
+        <v/>
+      </c>
+      <c r="G104" s="103">
+        <f>SUM(D104:F104)</f>
+        <v/>
+      </c>
+      <c r="H104" s="104">
+        <f>G104/$G$102-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" s="101" t="n">
+        <v>600</v>
+      </c>
+      <c r="C105" s="102">
+        <f>$B105*$C$13/Assumptions!$D$7/43560</f>
+        <v/>
+      </c>
+      <c r="D105" s="73">
+        <f>$C$93*$C$96/$B105</f>
+        <v/>
+      </c>
+      <c r="E105" s="73">
+        <f>$C$94*($B105/$C$97)^0.5*$C$96/$B105</f>
+        <v/>
+      </c>
+      <c r="F105" s="73">
+        <f>$C$95*($B105/$C$97)*$C$96/$B105</f>
+        <v/>
+      </c>
+      <c r="G105" s="103">
+        <f>SUM(D105:F105)</f>
+        <v/>
+      </c>
+      <c r="H105" s="104">
+        <f>G105/$G$102-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" s="101" t="n">
+        <v>900</v>
+      </c>
+      <c r="C106" s="102">
+        <f>$B106*$C$13/Assumptions!$D$7/43560</f>
+        <v/>
+      </c>
+      <c r="D106" s="73">
+        <f>$C$93*$C$96/$B106</f>
+        <v/>
+      </c>
+      <c r="E106" s="73">
+        <f>$C$94*($B106/$C$97)^0.5*$C$96/$B106</f>
+        <v/>
+      </c>
+      <c r="F106" s="73">
+        <f>$C$95*($B106/$C$97)*$C$96/$B106</f>
+        <v/>
+      </c>
+      <c r="G106" s="103">
+        <f>SUM(D106:F106)</f>
+        <v/>
+      </c>
+      <c r="H106" s="104">
+        <f>G106/$G$102-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>H.  EVERYTHING EXCEPT LAND  -  $ per stall, scale against specification</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="n"/>
+      <c r="C108" s="5" t="n"/>
+      <c r="D108" s="5" t="n"/>
+      <c r="E108" s="5" t="n"/>
+      <c r="F108" s="5" t="n"/>
+      <c r="G108" s="5" t="n"/>
+      <c r="H108" s="5" t="n"/>
+      <c r="I108" s="5" t="n"/>
+      <c r="J108" s="5" t="n"/>
+    </row>
+    <row r="109" ht="26" customHeight="1">
+      <c r="A109" s="19" t="inlineStr">
+        <is>
+          <t>Yard construction at the row's package + per-stall discrete items + non-land fixed cost. Excludes land, financing carry and the lease-up reserve, so it is not directly comparable to the all-in cost per stall on the Summary tab - it isolates the construction and site-cost levers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>Per-stall discrete items (lighting, electrical, cameras)</t>
+        </is>
+      </c>
+      <c r="B110" s="7" t="inlineStr">
+        <is>
+          <t>$ / stall</t>
+        </is>
+      </c>
+      <c r="C110" s="12">
+        <f>Capex_Variable!$D$20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="59" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="B111" s="60" t="inlineStr"/>
+      <c r="C111" s="80" t="n">
+        <v>150</v>
+      </c>
+      <c r="D111" s="80" t="n">
+        <v>216</v>
+      </c>
+      <c r="E111" s="80" t="n">
+        <v>300</v>
+      </c>
+      <c r="F111" s="80" t="n">
+        <v>450</v>
+      </c>
+      <c r="G111" s="80" t="n">
+        <v>600</v>
+      </c>
+      <c r="H111" s="7" t="inlineStr">
+        <is>
+          <t>stalls</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>Base section</t>
+        </is>
+      </c>
+      <c r="C112" s="105">
+        <f>(($C$28/(150*$C$13))+($D$25*MAX($C$35,((150*$C$13)/$C$15)^-$C$34))+((IF((150*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$C$36,$C$37,IF((150*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$D$36,$D$37,IF((150*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$E$36,$E$37,IF((150*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$F$36,$F$37,$G$37)))))/$C$38*$C$30+$C$31)+C$75)*$C$13+$C$110+($C$93+$C$94*(150/$C$97)^0.5+$C$95*(150/$C$97))*$C$96/150</f>
+        <v/>
+      </c>
+      <c r="D112" s="73">
+        <f>(($C$28/(216*$C$13))+($D$25*MAX($C$35,((216*$C$13)/$C$15)^-$C$34))+((IF((216*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$C$36,$C$37,IF((216*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$D$36,$D$37,IF((216*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$E$36,$E$37,IF((216*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$F$36,$F$37,$G$37)))))/$C$38*$C$30+$C$31)+C$75)*$C$13+$C$110+($C$93+$C$94*(216/$C$97)^0.5+$C$95*(216/$C$97))*$C$96/216</f>
+        <v/>
+      </c>
+      <c r="E112" s="73">
+        <f>(($C$28/(300*$C$13))+($D$25*MAX($C$35,((300*$C$13)/$C$15)^-$C$34))+((IF((300*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$C$36,$C$37,IF((300*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$D$36,$D$37,IF((300*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$E$36,$E$37,IF((300*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$F$36,$F$37,$G$37)))))/$C$38*$C$30+$C$31)+C$75)*$C$13+$C$110+($C$93+$C$94*(300/$C$97)^0.5+$C$95*(300/$C$97))*$C$96/300</f>
+        <v/>
+      </c>
+      <c r="F112" s="73">
+        <f>(($C$28/(450*$C$13))+($D$25*MAX($C$35,((450*$C$13)/$C$15)^-$C$34))+((IF((450*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$C$36,$C$37,IF((450*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$D$36,$D$37,IF((450*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$E$36,$E$37,IF((450*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$F$36,$F$37,$G$37)))))/$C$38*$C$30+$C$31)+C$75)*$C$13+$C$110+($C$93+$C$94*(450/$C$97)^0.5+$C$95*(450/$C$97))*$C$96/450</f>
+        <v/>
+      </c>
+      <c r="G112" s="73">
+        <f>(($C$28/(600*$C$13))+($D$25*MAX($C$35,((600*$C$13)/$C$15)^-$C$34))+((IF((600*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$C$36,$C$37,IF((600*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$D$36,$D$37,IF((600*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$E$36,$E$37,IF((600*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$F$36,$F$37,$G$37)))))/$C$38*$C$30+$C$31)+C$75)*$C$13+$C$110+($C$93+$C$94*(600/$C$97)^0.5+$C$95*(600/$C$97))*$C$96/600</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>A  Value-engineer</t>
+        </is>
+      </c>
+      <c r="C113" s="105">
+        <f>(($C$28/(150*$C$13))+($D$25*MAX($C$35,((150*$C$13)/$C$15)^-$C$34))+((IF((150*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$C$36,$C$37,IF((150*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$D$36,$D$37,IF((150*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$E$36,$E$37,IF((150*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$F$36,$F$37,$G$37)))))/$C$38*$C$30+$C$31)+D$75)*$C$13+$C$110+($C$93+$C$94*(150/$C$97)^0.5+$C$95*(150/$C$97))*$C$96/150</f>
+        <v/>
+      </c>
+      <c r="D113" s="73">
+        <f>(($C$28/(216*$C$13))+($D$25*MAX($C$35,((216*$C$13)/$C$15)^-$C$34))+((IF((216*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$C$36,$C$37,IF((216*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$D$36,$D$37,IF((216*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$E$36,$E$37,IF((216*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$F$36,$F$37,$G$37)))))/$C$38*$C$30+$C$31)+D$75)*$C$13+$C$110+($C$93+$C$94*(216/$C$97)^0.5+$C$95*(216/$C$97))*$C$96/216</f>
+        <v/>
+      </c>
+      <c r="E113" s="73">
+        <f>(($C$28/(300*$C$13))+($D$25*MAX($C$35,((300*$C$13)/$C$15)^-$C$34))+((IF((300*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$C$36,$C$37,IF((300*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$D$36,$D$37,IF((300*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$E$36,$E$37,IF((300*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$F$36,$F$37,$G$37)))))/$C$38*$C$30+$C$31)+D$75)*$C$13+$C$110+($C$93+$C$94*(300/$C$97)^0.5+$C$95*(300/$C$97))*$C$96/300</f>
+        <v/>
+      </c>
+      <c r="F113" s="73">
+        <f>(($C$28/(450*$C$13))+($D$25*MAX($C$35,((450*$C$13)/$C$15)^-$C$34))+((IF((450*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$C$36,$C$37,IF((450*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$D$36,$D$37,IF((450*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$E$36,$E$37,IF((450*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$F$36,$F$37,$G$37)))))/$C$38*$C$30+$C$31)+D$75)*$C$13+$C$110+($C$93+$C$94*(450/$C$97)^0.5+$C$95*(450/$C$97))*$C$96/450</f>
+        <v/>
+      </c>
+      <c r="G113" s="73">
+        <f>(($C$28/(600*$C$13))+($D$25*MAX($C$35,((600*$C$13)/$C$15)^-$C$34))+((IF((600*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$C$36,$C$37,IF((600*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$D$36,$D$37,IF((600*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$E$36,$E$37,IF((600*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$F$36,$F$37,$G$37)))))/$C$38*$C$30+$C$31)+D$75)*$C$13+$C$110+($C$93+$C$94*(600/$C$97)^0.5+$C$95*(600/$C$97))*$C$96/600</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="6" t="inlineStr">
+        <is>
+          <t>B  A + thin stalls</t>
+        </is>
+      </c>
+      <c r="C114" s="105">
+        <f>(($C$28/(150*$C$13))+($D$25*MAX($C$35,((150*$C$13)/$C$15)^-$C$34))+((IF((150*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$C$36,$C$37,IF((150*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$D$36,$D$37,IF((150*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$E$36,$E$37,IF((150*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$F$36,$F$37,$G$37)))))/$C$38*$C$30+$C$31)+E$75)*$C$13+$C$110+($C$93+$C$94*(150/$C$97)^0.5+$C$95*(150/$C$97))*$C$96/150</f>
+        <v/>
+      </c>
+      <c r="D114" s="73">
+        <f>(($C$28/(216*$C$13))+($D$25*MAX($C$35,((216*$C$13)/$C$15)^-$C$34))+((IF((216*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$C$36,$C$37,IF((216*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$D$36,$D$37,IF((216*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$E$36,$E$37,IF((216*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$F$36,$F$37,$G$37)))))/$C$38*$C$30+$C$31)+E$75)*$C$13+$C$110+($C$93+$C$94*(216/$C$97)^0.5+$C$95*(216/$C$97))*$C$96/216</f>
+        <v/>
+      </c>
+      <c r="E114" s="73">
+        <f>(($C$28/(300*$C$13))+($D$25*MAX($C$35,((300*$C$13)/$C$15)^-$C$34))+((IF((300*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$C$36,$C$37,IF((300*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$D$36,$D$37,IF((300*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$E$36,$E$37,IF((300*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$F$36,$F$37,$G$37)))))/$C$38*$C$30+$C$31)+E$75)*$C$13+$C$110+($C$93+$C$94*(300/$C$97)^0.5+$C$95*(300/$C$97))*$C$96/300</f>
+        <v/>
+      </c>
+      <c r="F114" s="73">
+        <f>(($C$28/(450*$C$13))+($D$25*MAX($C$35,((450*$C$13)/$C$15)^-$C$34))+((IF((450*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$C$36,$C$37,IF((450*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$D$36,$D$37,IF((450*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$E$36,$E$37,IF((450*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$F$36,$F$37,$G$37)))))/$C$38*$C$30+$C$31)+E$75)*$C$13+$C$110+($C$93+$C$94*(450/$C$97)^0.5+$C$95*(450/$C$97))*$C$96/450</f>
+        <v/>
+      </c>
+      <c r="G114" s="73">
+        <f>(($C$28/(600*$C$13))+($D$25*MAX($C$35,((600*$C$13)/$C$15)^-$C$34))+((IF((600*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$C$36,$C$37,IF((600*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$D$36,$D$37,IF((600*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$E$36,$E$37,IF((600*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$F$36,$F$37,$G$37)))))/$C$38*$C$30+$C$31)+E$75)*$C$13+$C$110+($C$93+$C$94*(600/$C$97)^0.5+$C$95*(600/$C$97))*$C$96/600</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t>C  Hybrid (S2)</t>
+        </is>
+      </c>
+      <c r="C115" s="105">
+        <f>(($C$28/(150*$C$13))+($D$25*MAX($C$35,((150*$C$13)/$C$15)^-$C$34))+((IF((150*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$C$36,$C$37,IF((150*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$D$36,$D$37,IF((150*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$E$36,$E$37,IF((150*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$F$36,$F$37,$G$37)))))/$C$38*$C$30+$C$31)+F$75)*$C$13+$C$110+($C$93+$C$94*(150/$C$97)^0.5+$C$95*(150/$C$97))*$C$96/150</f>
+        <v/>
+      </c>
+      <c r="D115" s="73">
+        <f>(($C$28/(216*$C$13))+($D$25*MAX($C$35,((216*$C$13)/$C$15)^-$C$34))+((IF((216*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$C$36,$C$37,IF((216*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$D$36,$D$37,IF((216*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$E$36,$E$37,IF((216*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$F$36,$F$37,$G$37)))))/$C$38*$C$30+$C$31)+F$75)*$C$13+$C$110+($C$93+$C$94*(216/$C$97)^0.5+$C$95*(216/$C$97))*$C$96/216</f>
+        <v/>
+      </c>
+      <c r="E115" s="73">
+        <f>(($C$28/(300*$C$13))+($D$25*MAX($C$35,((300*$C$13)/$C$15)^-$C$34))+((IF((300*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$C$36,$C$37,IF((300*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$D$36,$D$37,IF((300*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$E$36,$E$37,IF((300*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$F$36,$F$37,$G$37)))))/$C$38*$C$30+$C$31)+F$75)*$C$13+$C$110+($C$93+$C$94*(300/$C$97)^0.5+$C$95*(300/$C$97))*$C$96/300</f>
+        <v/>
+      </c>
+      <c r="F115" s="73">
+        <f>(($C$28/(450*$C$13))+($D$25*MAX($C$35,((450*$C$13)/$C$15)^-$C$34))+((IF((450*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$C$36,$C$37,IF((450*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$D$36,$D$37,IF((450*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$E$36,$E$37,IF((450*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$F$36,$F$37,$G$37)))))/$C$38*$C$30+$C$31)+F$75)*$C$13+$C$110+($C$93+$C$94*(450/$C$97)^0.5+$C$95*(450/$C$97))*$C$96/450</f>
+        <v/>
+      </c>
+      <c r="G115" s="73">
+        <f>(($C$28/(600*$C$13))+($D$25*MAX($C$35,((600*$C$13)/$C$15)^-$C$34))+((IF((600*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$C$36,$C$37,IF((600*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$D$36,$D$37,IF((600*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$E$36,$E$37,IF((600*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$F$36,$F$37,$G$37)))))/$C$38*$C$30+$C$31)+F$75)*$C$13+$C$110+($C$93+$C$94*(600/$C$97)^0.5+$C$95*(600/$C$97))*$C$96/600</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="6" t="inlineStr">
+        <is>
+          <t>D  Hybrid + all</t>
+        </is>
+      </c>
+      <c r="C116" s="105">
+        <f>(($C$28/(150*$C$13))+($D$25*MAX($C$35,((150*$C$13)/$C$15)^-$C$34))+((IF((150*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$C$36,$C$37,IF((150*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$D$36,$D$37,IF((150*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$E$36,$E$37,IF((150*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$F$36,$F$37,$G$37)))))/$C$38*$C$30+$C$31)+G$75)*$C$13+$C$110+($C$93+$C$94*(150/$C$97)^0.5+$C$95*(150/$C$97))*$C$96/150</f>
+        <v/>
+      </c>
+      <c r="D116" s="106">
+        <f>(($C$28/(216*$C$13))+($D$25*MAX($C$35,((216*$C$13)/$C$15)^-$C$34))+((IF((216*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$C$36,$C$37,IF((216*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$D$36,$D$37,IF((216*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$E$36,$E$37,IF((216*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$F$36,$F$37,$G$37)))))/$C$38*$C$30+$C$31)+G$75)*$C$13+$C$110+($C$93+$C$94*(216/$C$97)^0.5+$C$95*(216/$C$97))*$C$96/216</f>
+        <v/>
+      </c>
+      <c r="E116" s="106">
+        <f>(($C$28/(300*$C$13))+($D$25*MAX($C$35,((300*$C$13)/$C$15)^-$C$34))+((IF((300*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$C$36,$C$37,IF((300*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$D$36,$D$37,IF((300*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$E$36,$E$37,IF((300*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$F$36,$F$37,$G$37)))))/$C$38*$C$30+$C$31)+G$75)*$C$13+$C$110+($C$93+$C$94*(300/$C$97)^0.5+$C$95*(300/$C$97))*$C$96/300</f>
+        <v/>
+      </c>
+      <c r="F116" s="106">
+        <f>(($C$28/(450*$C$13))+($D$25*MAX($C$35,((450*$C$13)/$C$15)^-$C$34))+((IF((450*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$C$36,$C$37,IF((450*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$D$36,$D$37,IF((450*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$E$36,$E$37,IF((450*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$F$36,$F$37,$G$37)))))/$C$38*$C$30+$C$31)+G$75)*$C$13+$C$110+($C$93+$C$94*(450/$C$97)^0.5+$C$95*(450/$C$97))*$C$96/450</f>
+        <v/>
+      </c>
+      <c r="G116" s="106">
+        <f>(($C$28/(600*$C$13))+($D$25*MAX($C$35,((600*$C$13)/$C$15)^-$C$34))+((IF((600*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$C$36,$C$37,IF((600*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$D$36,$D$37,IF((600*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$E$36,$E$37,IF((600*$C$13)*($C$11*$C$9+$C$12*$C$10)&lt;=$F$36,$F$37,$G$37)))))/$C$38*$C$30+$C$31)+G$75)*$C$13+$C$110+($C$93+$C$94*(600/$C$97)^0.5+$C$95*(600/$C$97))*$C$96/600</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="48" t="inlineStr">
+        <is>
+          <t>Read across for scale, down for specification. Specification moves the yard number three to five times as far as volume does; non-land fixed cost moves further than either.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t>I.  WHAT DOES NOT SCALE, AND WHAT GETS WORSE</t>
+        </is>
+      </c>
+      <c r="B119" s="5" t="n"/>
+      <c r="C119" s="5" t="n"/>
+      <c r="D119" s="5" t="n"/>
+      <c r="E119" s="5" t="n"/>
+      <c r="F119" s="5" t="n"/>
+      <c r="G119" s="5" t="n"/>
+      <c r="H119" s="5" t="n"/>
+      <c r="I119" s="5" t="n"/>
+      <c r="J119" s="5" t="n"/>
+    </row>
+    <row r="120" ht="40" customHeight="1">
+      <c r="A120" s="76" t="inlineStr">
+        <is>
+          <t>- Stormwater treatment tracks impervious area almost exactly, and CT's industrial stormwater rules require a treatment train plus spill controls, not just detention. A bigger yard buys a bigger basin at the same unit cost. Pervious stall surfacing is the only real relief - which is a second, usually unmodelled, argument for the hybrid section.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="40" customHeight="1">
+      <c r="A121" s="76" t="inlineStr">
+        <is>
+          <t>- Asphalt haul radius is a hard constraint, not a volume question. HMA has to be placed hot, so a plant more than about 45 minutes out raises cost at any project size. Confirm the nearest plant before trusting any $/ton quote in this model.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="40" customHeight="1">
+      <c r="A122" s="76" t="inlineStr">
+        <is>
+          <t>- Yard lighting and stall electrical scale linearly with stall count. They are the per-stall discrete items and volume does nothing for them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="40" customHeight="1">
+      <c r="A123" s="76" t="inlineStr">
+        <is>
+          <t>- Bonding, builder's risk and construction management are percentages of hard cost, so they scale linearly by construction and never dilute.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="40" customHeight="1">
+      <c r="A124" s="76" t="inlineStr">
+        <is>
+          <t>- Larger sites cross permitting thresholds - wider traffic study scope, more CT DEEP attention, longer entitlement. Schedule risk rises with size even as cost per stall falls.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="40" customHeight="1">
+      <c r="A125" s="76" t="inlineStr">
+        <is>
+          <t>- Phasing REVERSES the mobilisation economy. Each phase re-mobilises every trade. Phase for capital or lease-up reasons, never expecting a construction saving.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A123:J123"/>
+    <mergeCell ref="A120:J120"/>
+    <mergeCell ref="A124:J124"/>
+    <mergeCell ref="A122:J122"/>
+    <mergeCell ref="A125:J125"/>
+    <mergeCell ref="A121:J121"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
